--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2031-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2031-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2A5E005-28E8-4D1B-A172-A1E09312A770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9201B0BA-56B2-4189-A4BB-64BBD8BB4B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{8D79B1A3-6ED4-4798-BCD4-7B6E4D5D4B5D}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{82CDE731-8C68-4761-879F-D6A398B0F182}"/>
   </bookViews>
   <sheets>
     <sheet name="2031-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1538,25 +1538,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AF23F97-6406-4801-8E45-A7FF2D36A534}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6057DFBF-A50B-4681-B71D-32819A66B551}">
   <dimension ref="A1:X39"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1590,7 +1589,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1626,7 +1625,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1678,7 +1677,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1746,7 +1745,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2024</v>
       </c>
@@ -1818,7 +1817,7 @@
         <v>6.97</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="38">
         <v>2023</v>
       </c>
@@ -1890,7 +1889,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="36">
         <v>2022</v>
       </c>
@@ -1962,7 +1961,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="38">
         <v>2021</v>
       </c>
@@ -2034,7 +2033,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="36">
         <v>2020</v>
       </c>
@@ -2106,7 +2105,7 @@
         <v>5.85</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="38">
         <v>2019</v>
       </c>
@@ -2178,7 +2177,7 @@
         <v>4.7300000000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="36">
         <v>2018</v>
       </c>
@@ -2250,7 +2249,7 @@
         <v>5.77</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="38">
         <v>2017</v>
       </c>
@@ -2322,7 +2321,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="36">
         <v>2016</v>
       </c>
@@ -2394,7 +2393,7 @@
         <v>8.57</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="38">
         <v>2015</v>
       </c>
@@ -2466,7 +2465,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="36">
         <v>2014</v>
       </c>
@@ -2538,7 +2537,7 @@
         <v>9.66</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="38">
         <v>2013</v>
       </c>
@@ -2610,7 +2609,7 @@
         <v>5.93</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="36">
         <v>2012</v>
       </c>
@@ -2682,7 +2681,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="38">
         <v>2011</v>
       </c>
@@ -2754,7 +2753,7 @@
         <v>6.13</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="36">
         <v>2010</v>
       </c>
@@ -2826,7 +2825,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="38">
         <v>2009</v>
       </c>
@@ -2898,7 +2897,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="36">
         <v>2008</v>
       </c>
@@ -2970,7 +2969,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="38">
         <v>2007</v>
       </c>
@@ -3042,7 +3041,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="36">
         <v>2006</v>
       </c>
@@ -3114,7 +3113,7 @@
         <v>7.73</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="38">
         <v>2005</v>
       </c>
@@ -3186,7 +3185,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="36">
         <v>2004</v>
       </c>
@@ -3258,7 +3257,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="38">
         <v>2003</v>
       </c>
@@ -3330,7 +3329,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="40">
         <v>2002</v>
       </c>
@@ -3402,7 +3401,7 @@
         <v>9.11</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="42"/>
       <c r="B28" s="43"/>
       <c r="C28" s="19" t="s">
@@ -3430,7 +3429,7 @@
       <c r="W28" s="49"/>
       <c r="X28" s="45"/>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2001</v>
       </c>
@@ -3502,7 +3501,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>2000</v>
       </c>
@@ -3574,7 +3573,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>1999</v>
       </c>
@@ -3646,7 +3645,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>1998</v>
       </c>
@@ -3718,7 +3717,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="38">
         <v>1997</v>
       </c>
@@ -3790,7 +3789,7 @@
         <v>8.89</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>1996</v>
       </c>
@@ -3862,7 +3861,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="38">
         <v>1995</v>
       </c>
@@ -3934,7 +3933,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>1994</v>
       </c>
@@ -4006,7 +4005,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="38">
         <v>1993</v>
       </c>
@@ -4078,7 +4077,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>1992</v>
       </c>
@@ -4150,7 +4149,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="38" t="s">
         <v>59</v>
       </c>
